--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N16_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.2459727987492</v>
+        <v>2.639970579796745</v>
       </c>
       <c r="D2" t="n">
-        <v>16.21717873962189</v>
+        <v>2.635291545188557</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
